--- a/backend/data/trading_bull.xlsx
+++ b/backend/data/trading_bull.xlsx
@@ -330,7 +330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -403,7 +403,7 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.02</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>87.16</v>
@@ -442,7 +442,7 @@
         <v>85</v>
       </c>
       <c r="F3" t="n">
-        <v>8.050000000000001</v>
+        <v>7.81</v>
       </c>
       <c r="G3" t="n">
         <v>70.78</v>
@@ -481,7 +481,7 @@
         <v>67</v>
       </c>
       <c r="F4" t="n">
-        <v>-14.08</v>
+        <v>-14.05</v>
       </c>
       <c r="G4" t="n">
         <v>51.57</v>
@@ -520,7 +520,7 @@
         <v>66</v>
       </c>
       <c r="F5" t="n">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="G5" t="n">
         <v>49.74</v>
@@ -559,7 +559,7 @@
         <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>-18.88</v>
+        <v>-18.84</v>
       </c>
       <c r="G6" t="n">
         <v>44.02</v>
@@ -586,26 +586,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>-13.83</v>
+        <v>-6.04</v>
       </c>
       <c r="G7" t="n">
-        <v>18.81</v>
+        <v>32.41</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑↑</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -625,26 +625,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>-9.94</v>
+        <v>-13.88</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7</v>
+        <v>18.81</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>→</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -664,22 +664,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>-13.97</v>
+        <v>-10.1</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -703,22 +703,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.75</v>
+        <v>-14.41</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.35</v>
+        <v>-0.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -751,17 +751,17 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>-22.74</v>
+        <v>-6.83</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.71</v>
+        <v>-1.35</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>↓→</t>
+          <t>→</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -781,22 +781,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>-20.89</v>
+        <v>-22.83</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.18</v>
+        <v>-6.71</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>-23.81</v>
+        <v>-20.87</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.62</v>
+        <v>-10.18</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -859,29 +859,68 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-23.82</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-12.62</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>↓→</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>ITC</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="n">
-        <v>-26.1</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="F15" t="n">
+        <v>-26.21</v>
+      </c>
+      <c r="G15" t="n">
         <v>-21.86</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/data/trading_bull.xlsx
+++ b/backend/data/trading_bull.xlsx
@@ -330,7 +330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -383,7 +383,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -391,22 +391,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.300000000000001</v>
+        <v>12.84</v>
       </c>
       <c r="G2" t="n">
-        <v>87.16</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -422,7 +422,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -430,22 +430,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F3" t="n">
-        <v>7.81</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>70.78</v>
+        <v>86.02</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -469,22 +469,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="F4" t="n">
-        <v>-14.05</v>
+        <v>16.21</v>
       </c>
       <c r="G4" t="n">
-        <v>51.57</v>
+        <v>72.69</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -500,7 +500,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -508,22 +508,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="F5" t="n">
-        <v>4.95</v>
+        <v>7.81</v>
       </c>
       <c r="G5" t="n">
-        <v>49.74</v>
+        <v>70.78</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -547,22 +547,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
-        <v>-18.84</v>
+        <v>-6.73</v>
       </c>
       <c r="G6" t="n">
-        <v>44.02</v>
+        <v>66.25</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -586,7 +586,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.04</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>32.41</v>
+        <v>65.31</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -625,26 +625,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Telecommunication</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="F8" t="n">
-        <v>-13.88</v>
+        <v>-17.47</v>
       </c>
       <c r="G8" t="n">
-        <v>18.81</v>
+        <v>63.17</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑↑</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -656,7 +656,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -664,26 +664,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="F9" t="n">
-        <v>-10.1</v>
+        <v>13.05</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>62.05</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>→</t>
+          <t>↑↑</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -695,7 +695,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -703,26 +703,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="F10" t="n">
-        <v>-14.41</v>
+        <v>1.72</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5</v>
+        <v>59.62</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>→</t>
+          <t>↑↑</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -751,17 +751,17 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.83</v>
+        <v>-1.72</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.35</v>
+        <v>56.41</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>→</t>
+          <t>↑↑</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -790,17 +790,17 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
-        <v>-22.83</v>
+        <v>4.08</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.71</v>
+        <v>51.66</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>↓→</t>
+          <t>↑↑</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -812,7 +812,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -820,26 +820,26 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
-        <v>-20.87</v>
+        <v>-14.05</v>
       </c>
       <c r="G13" t="n">
-        <v>-10.18</v>
+        <v>51.57</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>↓→</t>
+          <t>↑↑</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -859,26 +859,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="F14" t="n">
-        <v>-23.82</v>
+        <v>4.95</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.62</v>
+        <v>49.74</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>↓→</t>
+          <t>↑↑</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -898,29 +898,263 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F15" t="n">
-        <v>-26.21</v>
+        <v>-18.84</v>
       </c>
       <c r="G15" t="n">
-        <v>-21.86</v>
+        <v>44.02</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑↑</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>63</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="G16" t="n">
+        <v>43.76</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>↑↑</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="G17" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>↑↑</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>60</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="G18" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>↑↑</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-8.58</v>
+      </c>
+      <c r="G19" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>↑↑</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>58</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="G20" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>↑↑</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>58</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-16.68</v>
+      </c>
+      <c r="G21" t="n">
+        <v>37.22</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>↑↑</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
